--- a/main/ValueSet-bc-qualification-value-set.xlsx
+++ b/main/ValueSet-bc-qualification-value-set.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-30T21:39:06+00:00</t>
+    <t>2026-04-01T23:28:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -112,10 +112,10 @@
     <t>System URI</t>
   </si>
   <si>
+    <t>https://terminology.hlth.gov.bc.ca/ProviderLocationRegistry/CodeSystem/bc-credential-code-system</t>
+  </si>
+  <si>
     <t>http://fhir.infoway-inforoute.ca/CodeSystem/scpqual</t>
-  </si>
-  <si>
-    <t>https://terminology.hlth.gov.bc.ca/ProviderLocationRegistry/CodeSystem/bc-credential-code-system</t>
   </si>
 </sst>
 </file>
